--- a/artfynd/A 39981-2025 artfynd.xlsx
+++ b/artfynd/A 39981-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -908,6 +908,117 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128734217</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58059</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ekeby, Frustuna, Ekeby, Frustuna, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>629665</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6546296</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sophia Kloth</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sophia Kloth</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39981-2025 artfynd.xlsx
+++ b/artfynd/A 39981-2025 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>128734217</v>
       </c>
       <c r="B4" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39981-2025 artfynd.xlsx
+++ b/artfynd/A 39981-2025 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>128734217</v>
       </c>
       <c r="B4" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39981-2025 artfynd.xlsx
+++ b/artfynd/A 39981-2025 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>128734217</v>
       </c>
       <c r="B4" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39981-2025 artfynd.xlsx
+++ b/artfynd/A 39981-2025 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>128734217</v>
       </c>
       <c r="B4" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39981-2025 artfynd.xlsx
+++ b/artfynd/A 39981-2025 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>128734217</v>
       </c>
       <c r="B4" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39981-2025 artfynd.xlsx
+++ b/artfynd/A 39981-2025 artfynd.xlsx
@@ -675,46 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62940855</v>
+        <v>98771702</v>
       </c>
       <c r="B2" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107868</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224363</v>
+        <v>1855</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Åkerkulla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Anthemis arvensis</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ekeby, 400 m SSO om, Srm</t>
+          <t>Grundet, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629620.6297830959</v>
+        <v>629611</v>
       </c>
       <c r="R2" t="n">
-        <v>6546356.064785161</v>
+        <v>6546346</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -741,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-01-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1984-07-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-01-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1984-07-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>riklig</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>åkerträda</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -788,53 +782,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98771702</v>
+        <v>128734217</v>
       </c>
       <c r="B3" t="n">
-        <v>104790</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1855</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Åkerkulla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthemis arvensis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grundet, Srm</t>
+          <t>Ekeby, Frustuna, Ekeby, Frustuna, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629610.6531330942</v>
+        <v>629665</v>
       </c>
       <c r="R3" t="n">
-        <v>6546345.941723971</v>
+        <v>6546296</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,27 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1984-07-19</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1984-07-19</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>riklig</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,30 +878,25 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>åkerträda</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Sophia Kloth</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Sophia Kloth</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128734217</v>
+        <v>62940855</v>
       </c>
       <c r="B4" t="n">
-        <v>58097</v>
+        <v>97985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,41 +904,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>224363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ekeby, Frustuna, Ekeby, Frustuna, Srm</t>
+          <t>Ekeby, 400 m SSO om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629665</v>
+        <v>629621</v>
       </c>
       <c r="R4" t="n">
-        <v>6546296</v>
+        <v>6546356</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2017-01-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2017-01-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,15 +971,20 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sophia Kloth</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sophia Kloth</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 39981-2025 artfynd.xlsx
+++ b/artfynd/A 39981-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98771702</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128734217</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,8 +1003,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62940855</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>